--- a/PO_TBD_20260629.xlsx
+++ b/PO_TBD_20260629.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -694,16 +694,16 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>12</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -776,7 +776,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>TAB BETASERC (BETAHISTINE) 24MG ABBOTT</t>
+          <t>TAB NOVOMIN (DIMENHYDRINATE) 50MG XEPA</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -793,13 +793,13 @@
         <v>0</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>1.62</v>
+        <v>0.28</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>81</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="16">
@@ -808,7 +808,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>SYR SEDILIX-RX LINCTUS (DEXTROMETHORPHAN 15MG/ PROMETHAZINE 3.125MG/ PHENYLEPHRINE 5MG EVERY 5ML)  90ML XEPA</t>
+          <t>TAB BETASERC (BETAHISTINE) 24MG ABBOTT</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -818,20 +818,20 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>5.9</v>
+        <v>1.62</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>59</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17">
@@ -840,7 +840,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>AXCEL UREA (UREA 10% W/W) CREAM 20G KOTRA PHARMA</t>
+          <t>SYR SEDILIX-RX LINCTUS (DEXTROMETHORPHAN 15MG/ PROMETHAZINE 3.125MG/ PHENYLEPHRINE 5MG EVERY 5ML)  90ML XEPA</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -850,20 +850,20 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E17" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>12</v>
+        <v>5.9</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
@@ -872,7 +872,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>SMECTA (DIOSMECTITE 3G) ORANGE-VANILLA POWDER SACHETS ZUELLIG</t>
+          <t>AXCEL UREA (UREA 10% W/W) CREAM 20G KOTRA PHARMA</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -882,20 +882,20 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>SACHET</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>1.66</v>
+        <v>12</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>91.3</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19">
@@ -904,7 +904,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>INJ HYALGAN ( HYALURONIC ACID ) 20MG/2ML PE PHARMA</t>
+          <t>SMECTA (DIOSMECTITE 3G) ORANGE-VANILLA POWDER SACHETS ZUELLIG</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -914,20 +914,20 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>SACHET</t>
         </is>
       </c>
       <c r="E19" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>118</v>
+        <v>1.66</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>590</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="20">
@@ -936,7 +936,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>IVD N/S 0.9% 500ML B. BRAUN</t>
+          <t>INJ HYALGAN ( HYALURONIC ACID ) 20MG/2ML PE PHARMA</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -953,13 +953,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>3.8</v>
+        <v>118</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>38</v>
+        <v>590</v>
       </c>
     </row>
     <row r="21">
@@ -968,7 +968,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>SYR BENA EXPECTORANT(DIPHENHYDRAMINE 14MG, AMMONIUM CHLORIDE 135MG/5ML) 90ML XEPA</t>
+          <t>IVD N/S 0.9% 500ML B. BRAUN</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="E21" s="8" t="n">
@@ -988,10 +988,10 @@
         <v>10</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TAB COAPROVEL  (IRBESARTAN/HYDROCHLOROTHIAZIDE) 300MG/12.5MG SANOFI</t>
+          <t>SYR BENA EXPECTORANT(DIPHENHYDRAMINE 14MG, AMMONIUM CHLORIDE 135MG/5ML) 90ML XEPA</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1010,20 +1010,20 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>101.2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>INFUSOL N/S 250ML (SODIUM CHLORIDE 0.9% ) AIN MEDICARE</t>
+          <t>TAB COAPROVEL  (IRBESARTAN/HYDROCHLOROTHIAZIDE) 300MG/12.5MG SANOFI</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -1042,20 +1042,20 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E23" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>4.85</v>
+        <v>2.3</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>38.8</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="24">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>IVD HARTMANN'S SOLUTION 500ML B. BRAUN</t>
+          <t>INFUSOL N/S 250ML (SODIUM CHLORIDE 0.9% ) AIN MEDICARE</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -1078,16 +1078,16 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>3.7</v>
+        <v>4.85</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>88.8</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="25">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>EFF GRANULES AVOSODA (SODIUM BICARBONATE) 1.916G/SACHET ABIO</t>
+          <t>IVD HARTMANN'S SOLUTION 500ML B. BRAUN</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -1106,20 +1106,20 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>SACHET</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="E25" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>101</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="26">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>KEZORAL (KETOCONAZOLE 2% W/W) CREAM 15G DUOPHARMA</t>
+          <t>EFF GRANULES AVOSODA (SODIUM BICARBONATE) 1.916G/SACHET ABIO</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1138,20 +1138,20 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>SACHET</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>7.7</v>
+        <v>1.01</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>53.9</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>VICIDE CREAM 5%  (ACYCLOVIR 15MG/G) 10G PAHANG</t>
+          <t>KEZORAL (KETOCONAZOLE 2% W/W) CREAM 15G DUOPHARMA</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -1177,13 +1177,13 @@
         <v>0</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>7.45</v>
+        <v>7.7</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>37.25</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="28">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>APPETON MV LYSINE SYRUP 120ML (VITAMIN A 1000IU + VITAMIN D3 200IU + VITAMIN B1 0.5MG + VITAMIN B2 0.5MG + VITAMIN B6 0.5MG + VITAMIN E 5IU + NICOTINAMIDE 6MG + PANTOTHENIC ACID 2MG + LYSINE 80MG) KOTRA PHARMA</t>
+          <t>VICIDE CREAM 5%  (ACYCLOVIR 15MG/G) 10G PAHANG</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -1202,20 +1202,20 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>39.04</v>
+        <v>7.45</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>117.12</v>
+        <v>37.25</v>
       </c>
     </row>
     <row r="29">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>AEVA THYMOL GARGLE 120ML APEX</t>
+          <t>APPETON MV LYSINE SYRUP 120ML (VITAMIN A 1000IU + VITAMIN D3 200IU + VITAMIN B1 0.5MG + VITAMIN B2 0.5MG + VITAMIN B6 0.5MG + VITAMIN E 5IU + NICOTINAMIDE 6MG + PANTOTHENIC ACID 2MG + LYSINE 80MG) KOTRA PHARMA</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>5.3</v>
+        <v>39.04</v>
       </c>
       <c r="H29" s="10" t="n">
-        <v>31.8</v>
+        <v>117.12</v>
       </c>
     </row>
     <row r="30">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>SCABOMA LOTION  ( LINDANE 1% ) GLENMARK</t>
+          <t>AEVA THYMOL GARGLE 120ML APEX</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -1273,13 +1273,13 @@
         <v>0</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>17.5</v>
+        <v>5.3</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>35</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="31">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>TAB JARDIANCE ( EMPAGLIFLOZIN ) 25MG BOEHRINGER</t>
+          <t>SCABOMA LOTION  ( LINDANE 1% ) GLENMARK</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -1298,20 +1298,20 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E31" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>5.07</v>
+        <v>17.5</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>152.1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>S/C MOUNJARO (TIRZEPATIDE 25MG/ML) 2.5MG DOSE LILLY</t>
+          <t>TAB JARDIANCE ( EMPAGLIFLOZIN ) 25MG BOEHRINGER</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -1330,20 +1330,20 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>103.67</v>
+        <v>5.07</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>2280.74</v>
+        <v>152.1</v>
       </c>
     </row>
     <row r="33">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>INJ MENQUADFI (MENINGOCOCCAL VACCINE) 0.5ML 1D SANOFI</t>
+          <t>S/C MOUNJARO (TIRZEPATIDE 25MG/ML) 2.5MG DOSE LILLY</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -1366,16 +1366,16 @@
         </is>
       </c>
       <c r="E33" s="8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>97</v>
+        <v>103.67</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>97</v>
+        <v>2384.41</v>
       </c>
     </row>
     <row r="34">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>TAB EUTHYROX (LEVOTHYROXINE SODIUM) 100MCG MERCK</t>
+          <t>INJ MENQUADFI (MENINGOCOCCAL VACCINE) 0.5ML 1D SANOFI</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1394,20 +1394,20 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>0.53</v>
+        <v>97</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>53</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>PNEUMOVAX 23 ( PNEUMOCOCCAL VACCINE POLYVALENT) MSD</t>
+          <t>TAB EUTHYROX (LEVOTHYROXINE SODIUM) 100MCG MERCK</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -1426,20 +1426,20 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E35" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="G35" s="10" t="n">
-        <v>106.5</v>
+        <v>0.53</v>
       </c>
       <c r="H35" s="10" t="n">
-        <v>532.5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>TAB EXFORGE 5/80 (AMLODIPINE 5MG/ VALSARTAN 80MG) NORVATIS</t>
+          <t>PNEUMOVAX 23 ( PNEUMOCOCCAL VACCINE POLYVALENT) MSD</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -1458,20 +1458,20 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>2.01</v>
+        <v>106.5</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>72.36</v>
+        <v>532.5</v>
       </c>
     </row>
     <row r="37">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>FIX DERMA MOISTURIZING CREAM FOR DRY SKIN 60G SYNERRV</t>
+          <t>TAB EXFORGE 5/80 (AMLODIPINE 5MG/ VALSARTAN 80MG) NORVATIS</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -1490,20 +1490,20 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E37" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="G37" s="10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="H37" s="10" t="n">
-        <v>0</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="38">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>FIX DERMA SCAR GEL FOR SCAR 15ML SYNERRV</t>
+          <t>FIX DERMA MOISTURIZING CREAM FOR DRY SKIN 60G SYNERRV</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>SMA STEP 1 1.65KG (N15) WYETH NUTRITIONALS (SGPORE) PTE LTD</t>
+          <t>FIX DERMA SCAR GEL FOR SCAR 15ML SYNERRV</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>TIN</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E39" s="8" t="n">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>ENTEROGERMINA 2BCFU ORAL SUSPENSION 5ML OPELLA HEALTHCARE</t>
+          <t>SMA STEP 1 1.65KG (N15) WYETH NUTRITIONALS (SGPORE) PTE LTD</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -1586,20 +1586,20 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>BOX</t>
+          <t>TIN</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>77.7</v>
+        <v>0</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>621.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>INJ GARASENT (GENTAMICIN SULPHATE  80MG/2ML AMP) DUOPHARMA</t>
+          <t>ENTEROGERMINA 2BCFU ORAL SUSPENSION 5ML OPELLA HEALTHCARE</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -1618,20 +1618,20 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>AMPULE</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="E41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>2.35</v>
+        <v>77.7</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>23.5</v>
+        <v>621.6</v>
       </c>
     </row>
     <row r="42">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>CAP ESSENTIALSE MAX 600MG 30'S A.NATTERMANN &amp; CIE. GMBH</t>
+          <t>INJ GARASENT (GENTAMICIN SULPHATE  80MG/2ML AMP) DUOPHARMA</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -1650,20 +1650,20 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>AMPULE</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="43">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>TAB SHINTAMET (CIMETIDINE) 400MG Y.S.P.</t>
+          <t>CAP ESSENTIALSE MAX 600MG 30'S A.NATTERMANN &amp; CIE. GMBH</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -1682,20 +1682,20 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E43" s="8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F43" s="8" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="H43" s="10" t="n">
-        <v>45.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>SYR PREDSOLONE (PREDNISOLONE 2.5MG/5ML) 100ML DYNAPHARM</t>
+          <t>TAB SHINTAMET (CIMETIDINE) 400MG Y.S.P.</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -1714,20 +1714,20 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>3</v>
+        <v>0.58</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>TAB DELTACARBON (CHARCOAL) 250MG IMEKS</t>
+          <t>TAB ANTAROL (PROPRANOLOL) 40MG IMEKS</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -1750,16 +1750,16 @@
         </is>
       </c>
       <c r="E45" s="8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>0.44</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H45" s="10" t="n">
-        <v>27.72</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="46">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
+          <t>TAB GLUCOPHAGE XR 1000MG METFORMIN</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>METFORMIN</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>20</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>TAB VELOXIN (MECLOZINE 25MG/PYRIDOXINE 50MG) PHARM-D</t>
+          <t>PULMICORT (BUDESONIDE) RESPULE 1MG ASTRAZENECA</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -1810,20 +1810,20 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>RESPULE</t>
         </is>
       </c>
       <c r="E47" s="8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>1.06</v>
+        <v>10.26</v>
       </c>
       <c r="H47" s="10" t="n">
-        <v>33.92</v>
+        <v>61.56</v>
       </c>
     </row>
     <row r="48">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>INJ MALON ( METOCLOPRAMIDE ) 10MG/2ML DUOPHARMA</t>
+          <t>SYR PREDSOLONE (PREDNISOLONE 2.5MG/5ML) 100ML DYNAPHARM</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -1842,20 +1842,20 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>4.28</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
+          <t>TAB DELTACARBON (CHARCOAL) 250MG IMEKS</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -1881,13 +1881,13 @@
         <v>20</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>0.68</v>
+        <v>0.44</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>54.4</v>
+        <v>27.72</v>
       </c>
     </row>
     <row r="50">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>TAB DIAPO (DIAZEPAM) 5MG DUOPHARMA</t>
+          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -1916,10 +1916,10 @@
         <v>20</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>28.8</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="51">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>TAB ZITHROLIDE (AZITHROMYCIN)  500MG PHARMANIAGA</t>
+          <t>TAB VELOXIN (MECLOZINE 25MG/PYRIDOXINE 50MG) PHARM-D</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -1938,20 +1938,20 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>PACKET</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E51" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>5.5</v>
+        <v>1.06</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>38.5</v>
+        <v>33.92</v>
       </c>
     </row>
     <row r="52">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>SUPP VOREN (DICLOFENAC SODIUM) 25MG Y.S.P.</t>
+          <t>INJ MALON ( METOCLOPRAMIDE ) 10MG/2ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -1970,20 +1970,20 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>SUPPOSITORIES</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>1.66</v>
+        <v>2.14</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>16.6</v>
+        <v>8.56</v>
       </c>
     </row>
     <row r="53">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>TAB PLAVIX (CLOPIDOGREL) 75MG SANOFI</t>
+          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -2006,16 +2006,16 @@
         </is>
       </c>
       <c r="E53" s="8" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>6.94</v>
+        <v>0.68</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>430.28</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="54">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>TAB YASMIN (DROSPIRENONE 3MG/ ETHINYLESTRADIOL 0.03MG) BAYER</t>
+          <t>TAB DIAPO (DIAZEPAM) 5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -2038,16 +2038,16 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>2.33</v>
+        <v>1.44</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>48.93</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="55">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>SYRUP NOVOMIN (DIMENHYDRINATE) 15MG/5ML 60ML (ORANGE FLV) XEPA</t>
+          <t>TAB ZITHROLIDE (AZITHROMYCIN)  500MG PHARMANIAGA</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -2066,11 +2066,11 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>PACKET</t>
         </is>
       </c>
       <c r="E55" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" s="8" t="n">
         <v>7</v>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>TAB NORMATEN (ATENOLOL) 100MG XEPA</t>
+          <t>SUPP VOREN (DICLOFENAC SODIUM) 25MG Y.S.P.</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -2098,20 +2098,20 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>SUPPOSITORIES</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>0.52</v>
+        <v>1.66</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>12.48</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="57">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>TAB COAPROVEL (IRBESARTAN/ HYDROCHOLOTHIAZIDE) 150MG/12.5MG SANOFI</t>
+          <t>TAB PLAVIX (CLOPIDOGREL) 75MG SANOFI</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
@@ -2137,13 +2137,13 @@
         <v>28</v>
       </c>
       <c r="F57" s="8" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>1.82</v>
+        <v>6.94</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>43.68</v>
+        <v>430.28</v>
       </c>
     </row>
     <row r="58">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>TAB ZENTEL (ALBENDAZOLE) 200MG 2'S HALEON</t>
+          <t>TAB YASMIN (DROSPIRENONE 3MG/ ETHINYLESTRADIOL 0.03MG) BAYER</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -2162,20 +2162,20 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>PACKET</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>9.65</v>
+        <v>2.33</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>38.6</v>
+        <v>48.93</v>
       </c>
     </row>
     <row r="59">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>TAB ROWATINEX ( PINENE 31MG, CAMPHENE 31MG, CINEOL 3MG, FENCHONE 4MG, BORNEOL 10MG, ANETHOL 4MG ) DCH AURIGA</t>
+          <t>SYRUP NOVOMIN (DIMENHYDRINATE) 15MG/5ML 60ML (ORANGE FLV) XEPA</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -2194,20 +2194,20 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E59" s="8" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="F59" s="8" t="n">
-        <v>200</v>
+        <v>7</v>
       </c>
       <c r="G59" s="10" t="n">
-        <v>0.66</v>
+        <v>5.5</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>132</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="60">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>CREAM CLODERM (CLOBETASOL 0.05% W/W) 15G HOE</t>
+          <t>TAB NORMATEN (ATENOLOL) 100MG XEPA</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -2226,20 +2226,20 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>10.5</v>
+        <v>0.52</v>
       </c>
       <c r="H60" s="7" t="n">
-        <v>73.5</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="61">
@@ -2248,30 +2248,30 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>ALLERGOCROM  (SODIUM CROMOGLYCATE ) 2% EYE DROPS 10ML PHARMAFORTE URSAPHARM</t>
+          <t>TAB COAPROVEL (IRBESARTAN/ HYDROCHOLOTHIAZIDE) 150MG/12.5MG SANOFI</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>PHARMAFORTE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E61" s="8" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>16.5</v>
+        <v>1.82</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>115.5</v>
+        <v>43.68</v>
       </c>
     </row>
     <row r="62">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>AQUA CREAM (PARAFFIN, WHITE SOFT CREAM) 500GM DUOPHARMA</t>
+          <t>TAB ZENTEL (ALBENDAZOLE) 200MG 2'S HALEON</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -2290,20 +2290,20 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>JAR</t>
+          <t>PACKET</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>17</v>
+        <v>9.65</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>34</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="63">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>INJECSOL MgSO4 (Magnesium Sulfate 50% W/v 2.465G) 5ML VIAL AIN MEDICARE</t>
+          <t>TAB ROWATINEX ( PINENE 31MG, CAMPHENE 31MG, CINEOL 3MG, FENCHONE 4MG, BORNEOL 10MG, ANETHOL 4MG ) DCH AURIGA</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
@@ -2322,20 +2322,20 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="E63" s="8" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>20</v>
+        <v>0.66</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>60</v>
+        <v>132</v>
       </c>
     </row>
     <row r="64">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>INJ AMINOPHYLLIN 250MG/10ML FRESENIUS</t>
+          <t>SYR TUSSIDEX (DEXTROMETHORPHAN 15MG/5ML) 90ML XEPA</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -2354,20 +2354,20 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>INJ ACIPAN (ATROPINE SULPHATE) 1MG/ML 1ML DUOPHARMA</t>
+          <t>CREAM CLODERM (CLOBETASOL 0.05% W/W) 15G HOE</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
@@ -2386,20 +2386,20 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E65" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G65" s="10" t="n">
-        <v>2.32</v>
+        <v>10.5</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>18.56</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="66">
@@ -2408,30 +2408,30 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>A SCABS ( PERMETHRIN 5% ) LOTION 30ML HOE</t>
+          <t>ALLERGOCROM  (SODIUM CROMOGLYCATE ) 2% EYE DROPS 10ML PHARMAFORTE URSAPHARM</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PHARMAFORTE</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>11.6</v>
+        <v>16.5</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>104.4</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="67">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>T3 MYCIN LOTION (CLINDAMYCIN PHOSPHATE 1%) 30ML HOE</t>
+          <t>AQUA CREAM (PARAFFIN, WHITE SOFT CREAM) 500GM DUOPHARMA</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
@@ -2450,20 +2450,20 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>JAR</t>
         </is>
       </c>
       <c r="E67" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>243</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>KAOLIN-PECTIN (PECTIN 25MG/5ML, LIGHT KAOLIN 1G/5ML) 120ML DYNA</t>
+          <t>INJECSOL MgSO4 (Magnesium Sulfate 50% W/v 2.465G) 5ML VIAL AIN MEDICARE</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -2482,20 +2482,20 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F68" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F68" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="G68" s="7" t="n">
-        <v>4.64</v>
+        <v>20</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>32.48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>NITROSOL SUBLINGUAL AEROSOL SPRAY 400mcg/PER SPRAY VITAMODE</t>
+          <t>INJ AMINOPHYLLIN 250MG/10ML FRESENIUS</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
@@ -2514,20 +2514,20 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>SPRAY</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E69" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>55</v>
+        <v>8.5</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>110</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>GENGIGEL SPRAY ( SODIUM HYALURONATE 0.01% ) 20ML PHARMANIAGA</t>
+          <t>INJ ACIPAN (ATROPINE SULPHATE) 1MG/ML 1ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -2546,20 +2546,20 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>35</v>
+        <v>2.32</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>105</v>
+        <v>18.56</v>
       </c>
     </row>
     <row r="71">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>PREVENAR 13 (PNEUMOCOCCAL POLYSACCHARIDE CONJUGATE 13-VALENT) PFIZER</t>
+          <t>A SCABS ( PERMETHRIN 5% ) LOTION 30ML HOE</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
@@ -2578,20 +2578,20 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E71" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>219</v>
+        <v>11.6</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>876</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="72">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>SYR EMCOF-SF (HERBAL COUGH SYRUP) 100ML BioCare Pharmaceutical</t>
+          <t>T3 MYCIN LOTION (CLINDAMYCIN PHOSPHATE 1%) 30ML HOE</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -2610,20 +2610,20 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>6.2</v>
+        <v>27</v>
       </c>
       <c r="H72" s="7" t="n">
-        <v>6.2</v>
+        <v>243</v>
       </c>
     </row>
     <row r="73">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>INJ AMSUBAC (AMPICILLIN 1000MG/ SULBACTAM 500MG) 1.5 G AVERROES PHARMACEUTICALS SDN. BHD.</t>
+          <t>KAOLIN-PECTIN (PECTIN 25MG/5ML, LIGHT KAOLIN 1G/5ML) 120ML DYNA</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
@@ -2642,20 +2642,20 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>AMPULE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="E73" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G73" s="10" t="n">
-        <v>7.4</v>
+        <v>4.64</v>
       </c>
       <c r="H73" s="10" t="n">
-        <v>59.2</v>
+        <v>32.48</v>
       </c>
     </row>
     <row r="74">
@@ -2664,58 +2664,218 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
+          <t>NITROSOL SUBLINGUAL AEROSOL SPRAY 400mcg/PER SPRAY VITAMODE</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>SPRAY</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="H74" s="7" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>GENGIGEL SPRAY ( SODIUM HYALURONATE 0.01% ) 20ML PHARMANIAGA</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G75" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="H75" s="10" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>PREVENAR 13 (PNEUMOCOCCAL POLYSACCHARIDE CONJUGATE 13-VALENT) PFIZER</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>DOSE</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>219</v>
+      </c>
+      <c r="H76" s="7" t="n">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="n">
+        <v>68</v>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>SYR EMCOF-SF (HERBAL COUGH SYRUP) 100ML BioCare Pharmaceutical</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H77" s="10" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>INJ AMSUBAC (AMPICILLIN 1000MG/ SULBACTAM 500MG) 1.5 G AVERROES PHARMACEUTICALS SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>AMPULE</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H78" s="7" t="n">
+        <v>59.2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
           <t>TAB AUROXETIL 500 (Cefuroxime 500 Mg) Aurobindo Pharma</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>TABLET</t>
         </is>
       </c>
-      <c r="E74" s="5" t="n">
-        <v>340</v>
-      </c>
-      <c r="F74" s="5" t="n">
-        <v>160</v>
-      </c>
-      <c r="G74" s="7" t="n">
+      <c r="E79" s="8" t="n">
+        <v>320</v>
+      </c>
+      <c r="F79" s="8" t="n">
+        <v>180</v>
+      </c>
+      <c r="G79" s="10" t="n">
         <v>1.44</v>
       </c>
-      <c r="H74" s="7" t="n">
-        <v>230.4</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="11" t="inlineStr">
+      <c r="H79" s="10" t="n">
+        <v>259.2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="H75" s="12" t="n">
-        <v>9687.460000000001</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Total line items: 65</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Generated: 2026-06-29 08:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="13" t="inlineStr">
+      <c r="H80" s="12" t="n">
+        <v>10022.94</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Total line items: 70</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Generated: 2026-06-29 23:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="inlineStr">
         <is>
           <t>Note: Unit costs are from latest purchase price. Verify with supplier before confirming order.</t>
         </is>
@@ -2723,8 +2883,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A75:G75"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A80:G80"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
